--- a/AAPL_Dividends.xlsx
+++ b/AAPL_Dividends.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,6 +1150,14 @@
         <v>0.26</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
